--- a/data/dcea_prep/DCEA_donnees_preparatoires.xlsx
+++ b/data/dcea_prep/DCEA_donnees_preparatoires.xlsx
@@ -53,7 +53,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +126,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -488,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C22"/>
+  <dimension ref="B2:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9514,17 +9525,21 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Aucune enquête nationale identifiée</t>
+          <t>Confirmé absent — recherche 'tension artérielle/hypertension/diabète/glycémie' infructueuse également, aucun module santé mentale</t>
         </is>
       </c>
       <c r="K2" s="10" t="n"/>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>Santé mentale non couverte par EDS/STEPS Sénégal — hypothèse par défaut (distribution égale) à documenter</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="9" t="n"/>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent — recherche 'tension artérielle/hypertension/diabète/glycémie' infructueuse également, aucun module santé mentale</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Recherché (santé mentale), non trouvé dans ce document. Hypothèse par défaut (distribution égale) à documenter comme limite.</t>
+        </is>
+      </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9556,17 +9571,21 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Aucune enquête nationale identifiée</t>
+          <t>Confirmé absent</t>
         </is>
       </c>
       <c r="K3" s="10" t="n"/>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>Idem anxiété — hypothèse par défaut à documenter</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="9" t="n"/>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Idem anxiété — recherché, non trouvé. Hypothèse par défaut à documenter.</t>
+        </is>
+      </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9598,17 +9617,21 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>STEPS Sénégal (OMS)</t>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
         </is>
       </c>
       <c r="K4" s="10" t="n"/>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Prévalence diabète / glycémie élevée par quintile ou niveau d'éducation</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="9" t="n"/>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Recherché ('diabète', 'glycémie') : aucun module de dépistage des maladies non transmissibles dans ce document. Se référer à STEPS Sénégal (OMS) si disponible.</t>
+        </is>
+      </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9629,31 +9652,51 @@
       <c r="C5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
+      <c r="D5" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>22.3</v>
+      </c>
       <c r="I5" s="7">
         <f>SUM(D5:H5)</f>
         <v/>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>Santé de l'enfant : prévalence et traitement de la diarrhée (&lt;5 ans) par quintile de richesse</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="n"/>
-      <c r="N5" s="9" t="n"/>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 10.9 — Enfants &lt;5 ans ayant eu la diarrhée (2 semaines précédentes)</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>p.148 (PDF p.174)</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>Part de cas calculée à partir des taux de prévalence de la diarrhée par quintile (17,6% / 21,3% / 24,0% / 24,3% / 25,0%), rapportés à leur somme — les quintiles ayant une taille de population égale par construction, la part de cas = taux / somme des taux.</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -9682,17 +9725,21 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>EDS-Continue Sénégal</t>
+          <t>Anémie mentionnée en indicateur clé national uniquement (pas de table par quintile)</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>Anémie chez la femme/l'enfant (dosage hémoglobine) par quintile de richesse</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="9" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>Anémie mentionnée en indicateur clé national uniquement (pas de table par quintile)</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Recherché ('anémie') : ce document ne contient qu'un chiffre national synthétique dans le tableau des indicateurs clés (mention 'Prévalence de l'anémie parmi les femmes'), sans table détaillée par quintile — le test d'hémoglobine (biomarqueur) et sa restitution détaillée par sous-groupe ne semblent pas inclus dans cet extrait. Vérifier si un volume séparé du rapport EDS-Continue (biomarqueurs) existe.</t>
+        </is>
+      </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9724,17 +9771,21 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>EDS-Continue Sénégal (volet sérologie VIH)</t>
+          <t>Non trouvé : pas de volet sérologie VIH dans ce document</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>VIH/SIDA : séroprévalence par quintile de richesse</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="n"/>
-      <c r="N7" s="9" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Non trouvé : pas de volet sérologie VIH dans ce document</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Recherché (VIH/séroprévalence) : ce document ne contient pas de test biomarqueur VIH par quintile — l'EDS-Continue est un round annuel allégé, généralement sans volet sérologique (à la différence de l'EDS complète tous les 5 ans). Seule la couverture du TEST est disponible par quintile (onglet 3, indicateur E10) — utilisable comme proxy d'accès, pas de prévalence.</t>
+        </is>
+      </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9766,17 +9817,21 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>STEPS Sénégal (OMS)</t>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>Facteurs de risque cardiovasculaire (tension artérielle) par quintile ou niveau d'éducation</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="9" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Recherché ('tension artérielle', 'hypertension') : aucun module cardiovasculaire dans ce document. Se référer à STEPS Sénégal (OMS).</t>
+        </is>
+      </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9839,31 +9894,51 @@
       <c r="C10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+      <c r="D10" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>21.1</v>
+      </c>
       <c r="I10" s="7">
         <f>SUM(D10:H10)</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>Paludisme : prévalence (TDR positif) chez les enfants &lt;5 ans par quintile de richesse</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="9" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 12.10 — Enfants &lt;5 ans ayant eu de la fièvre (proxy palustre)</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>p.178 (PDF p.204)</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>PROXY : prévalence de la fièvre chez les &lt;5 ans (14,8/19,4/24,1/27,9/23,0%), le paludisme confirmé par test ne concernant que 15,7% des cas fébriles en moyenne (même tableau). À défaut d'une prévalence palustre confirmée par quintile dans ce document, la fièvre sert de proxy de charge, comme couramment fait en zone d'endémie.</t>
+        </is>
+      </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -9892,17 +9967,21 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>EDS-Continue Sénégal</t>
+          <t>Pas de table de prévalence des complications par quintile trouvée</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>Santé de la reproduction : complications de grossesse/accouchement, ou proxy inverse via CPN4/accouchement assisté par quintile</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="n"/>
-      <c r="N11" s="9" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>Pas de table de prévalence des complications par quintile trouvée</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Recherché : aucune table de prévalence des complications de grossesse/accouchement par quintile identifiée dans ce document. Les indicateurs d'ACCÈS sont en revanche solides : CPN4 (onglet 3, E02) et accouchement assisté (E03). Option : hypothèse de prévalence égale par quintile en première approche, l'essentiel du gradient d'équité venant alors du côté utilisation (E).</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9934,17 +10013,21 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>EDS-Continue Sénégal</t>
+          <t>Pas de prévalence rougeole (maladie rare) — voir couverture vaccinale (onglet 3)</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>Couverture vaccinale rougeole (VAR1) par quintile — utiliser comme proxy de non-exposition</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="9" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Pas de prévalence rougeole (maladie rare) — voir couverture vaccinale (onglet 3)</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Sans objet pour la prévalence (maladie évitée par la vaccination, peu de cas observés en enquête ménage). Le gradient d'équité passe par la couverture vaccinale RR/ROR (Tableau 10.4, p.142/PDF p.166) — présente mais non extraite ici (voir note onglet 3, E05).</t>
+        </is>
+      </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -9965,31 +10048,51 @@
       <c r="C13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="D13" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>17.1</v>
+      </c>
       <c r="I13" s="7">
         <f>SUM(D13:H13)</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>Mortalité néonatale par quintile de richesse (tableau mortalité des enfants)</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="9" t="n"/>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 8.3 — Mortalité néonatale (pour 1 000 naissances), 10 ans avant l'enquête</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>p.110 (PDF p.136)</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Part calculée à partir des quotients de mortalité néonatale par quintile (29/29/25/14/20 pour 1 000). Profil NON monotone (Q2≈Q1 plus pauvre, Q4&lt;Q5) — donnée réelle observée, pas une hypothèse de gradient régulier ; à ne pas lisser artificiellement.</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10018,17 +10121,21 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>STEPS Sénégal (OMS)</t>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
         </is>
       </c>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>Idem maladies cardiovasculaires — proxy hypertension par quintile</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="9" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent de l'EDS-Continue 2023</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>Idem maladies cardiovasculaires — recherché, non trouvé. Se référer à STEPS Sénégal (OMS), proxy hypertension.</t>
+        </is>
+      </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -10060,17 +10167,21 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Programme National de lutte contre la Tuberculose (PNT) / rapport annuel</t>
+          <t>Confirmé absent — aucun module EDS dédié</t>
         </is>
       </c>
       <c r="K15" s="10" t="n"/>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>Pas de module EDS dédié — utiliser notification de cas par région/pauvreté ou hypothèse par défaut (cf. Box 2 Arnold et al.)</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="9" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>Confirmé absent — aucun module EDS dédié</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Recherché, non trouvé. Confirme la note initiale : utiliser le rapport annuel du Programme National de lutte contre la Tuberculose (PNT), ou une hypothèse de distribution égale à documenter comme limite (cf. Box 2, Arnold et al. 2020).</t>
+        </is>
+      </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -10194,22 +10305,42 @@
           <t>Femmes de 15-49 ans en union utilisant une méthode moderne, par quintile</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
+      <c r="D2" s="12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>p.94 (PDF p.120)</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 7.4.2, colonne 'Une méthode moderne', femmes 15-49 ans en union.</t>
+        </is>
+      </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10229,22 +10360,42 @@
           <t>Femmes ayant eu 4+ CPN pour la dernière naissance, par quintile</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
+      <c r="D3" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>p.114-115 (PDF p.140-141)</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 9.2, colonne '4 visites prénatales ou plus', naissances vivantes des 2 ans précédant l'enquête.</t>
+        </is>
+      </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10264,22 +10415,42 @@
           <t>Naissances assistées par personnel de santé qualifié, par quintile</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="D4" s="12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>p.124-125 (PDF p.150-151)</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 9.9, colonne 'Pourcentage dont l'accouchement a été assisté par un prestataire qualifié'.</t>
+        </is>
+      </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10345,8 +10516,16 @@
         </is>
       </c>
       <c r="J6" s="7" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="9" t="n"/>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>p.142 (PDF p.166)</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>Données présentes (Tableau 10.4) mais structure à en-têtes multi-niveaux (doses 1/2/3 imbriquées par antigène, deux cohortes 12-23 et 24-35 mois) : extraction automatique fiable non réalisée pour éviter une erreur de colonne. Lecture manuelle directe recommandée pour la colonne 'Complètement vacciné (conformément au calendrier national)'.</t>
+        </is>
+      </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -10369,22 +10548,42 @@
           <t>Enfants avec diarrhée ayant reçu SRO/zinc, par quintile</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="9" t="n"/>
+      <c r="D7" s="12" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>p.148 (PDF p.174)</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 10.9, colonne 'Pourcentage pour lesquels des conseils ou un traitement ont été recherchés' (toutes sources). Mesure le recours général, pas spécifiquement le traitement SRO/zinc (Tableau 10.11, non extrait) — à affiner si un indicateur plus spécifique est requis.</t>
+        </is>
+      </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10415,8 +10614,12 @@
         </is>
       </c>
       <c r="J8" s="7" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="9" t="n"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>Recherché : aucun tableau distinct 'IRA/symptômes respiratoires' identifié dans cet extrait (le Tableau 10.8 porte sur la fièvre en général, déjà utilisé comme proxy pour le paludisme dans l'onglet 2 — éviter de le réutiliser ici sans vérification). Vérifier directement dans le rapport complet si un tableau IRA existe (chapitre 10).</t>
+        </is>
+      </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
           <t>À rechercher</t>
@@ -10439,22 +10642,42 @@
           <t>Enfants fébriles testés/traités pour le paludisme, par quintile</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>p.178 (PDF p.204)</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 12.10, colonne 'Pourcentage pour lesquels on a prélevé du sang au doigt/talon pour être testé' (parmi enfants &lt;5 ans fébriles). Alternative disponible dans la même table : '% diagnostiqué positif par un prestataire' (9,6/8,9/10,1/7,0/5,5%) — non retenue ici car reflète la positivité réelle autant que l'accès.</t>
+        </is>
+      </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10732,42 @@
           <t>Population ayant déjà fait un test VIH et reçu le résultat, par quintile</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>EDS-Continue Sénégal (à confirmer)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="D11" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>EDS-Continue Sénégal 2023</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>p.187 (PDF p.213)</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>Tableau 13.5.1, colonne 'Pourcentage ayant déjà fait un test du VIH', FEMMES 15-49 ans uniquement. Tableau 13.5.2 (Homme) disponible séparément si une moyenne pondérée par sexe est souhaitée.</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>À rechercher</t>
+          <t>Rempli</t>
         </is>
       </c>
     </row>
@@ -10851,13 +11094,13 @@
       <c r="H2" s="7" t="n"/>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>% de recours à une structure de santé publique/confessionnelle, toutes maladies confondues, par quintile de richesse (proxy de la distribution marginale du coût d'opportunité, méthode Arnold et al. 2020)</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="n"/>
+          <t>Recherché mais non trouvé sous cette forme précise dans l'EDS-Continue 2023 : aucune table agrégée 'recours à une structure publique, toutes maladies confondues, par quintile' n'a été identifiée (les tables de recours aux soins — diarrhée, fièvre, accouchement — ne ventilent pas systématiquement secteur public/privé ET quintile dans la même ligne). Recommandation : consulter l'EHCVM (module santé, Enquête Harmonisée sur les Conditions de Vie des Ménages), qui documente typiquement le type de prestataire consulté par quintile.</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Ce taux sert à répartir le coût d'opportunité (budget déplacé), indépendamment de l'intervention évaluée — cf. onglet 1_Lisez-moi.</t>
+          <t>À DÉFAUT : les indicateurs de recours déjà remplis (onglet 3 : diarrhée E06, paludisme E08, CPN4 E02, accouchement E03) donnent tous un gradient croissant net avec la richesse — un proxy de repli simple serait la MOYENNE de ces taux de recours par quintile, à documenter explicitement comme approximation si l'EHCVM n'est pas disponible.</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
